--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,75 +559,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비오엠 안양점 PT 헬스 필라테스</t>
+          <t>김관장의착한PT 관양동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitnessbom2@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1371-5144</t>
+          <t>0507-1475-3481</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnFnxeK</t>
+          <t>https://www.instagram.com/5director.kim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wit2oyw</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>1508</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="n">
-        <v>1151</v>
+        <v>412</v>
       </c>
       <c r="R2" t="n">
-        <v>2659</v>
+        <v>491</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1685119758</t>
+          <t>2033189234</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685119758</t>
+          <t>https://m.place.naver.com/place/2033189234</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>골드에이피트니스 안양점 헬스 PT 필라테스</t>
+          <t>김관장의착한PT 호계동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>goldaaa2020@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1369-0183</t>
+          <t>0507-1393-3519</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 283 안양빌딩 7층</t>
+          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goldaaa2020</t>
+          <t>https://blog.naver.com/thekindpt2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,28 +704,32 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5trfo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>1160</v>
+        <v>1793</v>
       </c>
       <c r="Q3" t="n">
-        <v>1073</v>
+        <v>672</v>
       </c>
       <c r="R3" t="n">
-        <v>2233</v>
+        <v>2465</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,56 +738,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1160243355</t>
+          <t>1954358336</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160243355</t>
+          <t>https://m.place.naver.com/place/1954358336</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비오엠 범계점 PT 헬스</t>
+          <t>비오엠 안양점 PT 헬스 필라테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitnessbom@naver.com</t>
+          <t>fitnessbom2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1374-5144</t>
+          <t>0507-1371-5144</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbom</t>
+          <t>https://pf.kakao.com/_xnFnxeK</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,18 +797,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cnd9</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1259</v>
+        <v>1516</v>
       </c>
       <c r="Q4" t="n">
-        <v>1338</v>
+        <v>1156</v>
       </c>
       <c r="R4" t="n">
-        <v>2597</v>
+        <v>2672</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1206984359</t>
+          <t>1685119758</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206984359</t>
+          <t>https://m.place.naver.com/place/1685119758</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아루카 PT&amp;필라테스 안양역점</t>
+          <t>비오엠 범계점 PT 헬스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tkakrnlxla@naver.com</t>
+          <t>fitnessbom@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1349-6494</t>
+          <t>0507-1374-5144</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 태평로60번길 42 407호</t>
+          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/arukah_anyang?igsh=MTN5Z21nMjA4ZHU4Yg%3D%3D&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/fitnessbom</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -883,15 +895,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cd0d</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>155</v>
+        <v>1264</v>
       </c>
       <c r="Q5" t="n">
-        <v>707</v>
+        <v>1356</v>
       </c>
       <c r="R5" t="n">
-        <v>862</v>
+        <v>2620</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +934,35 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1732851125</t>
+          <t>1206984359</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1732851125</t>
+          <t>https://m.place.naver.com/place/1206984359</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>핏해짐 PT헬스 범계점</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>fithae_gym@naver.com</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1400-3327</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 19 6층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fithae_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1184</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,35 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1419479860</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419479860</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>제이퍼스널트레이닝 PT 범계점</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>createfit@naver.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1352-0500</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로 221 센터프라자 3층 301호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/createfit</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,12 +1050,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,17 +1071,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>826</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1090,35 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1290214269</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290214269</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>아루카PT&amp;필라테스 평촌점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>tkakrnlxla@naver.com</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1311-6494</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 시민대로 280 3층 308호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tkakrnlxla</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1160,12 +1128,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1153,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1168,35 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1430031636</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1430031636</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>윈짐 PT 평촌본점</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dhormseldi@naver.com</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1363-6509</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 벌말로 42 2층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dhormseldi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,12 +1206,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1227,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>941</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1107</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,66 +1246,50 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1933799665</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933799665</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>레몬짐 안양점 PT&amp;헬스</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>lafcompany_@naver.com</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>031-441-7779</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.lemongym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,22 +1300,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1524</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1324,35 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1417153496</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417153496</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>온포인트 기능운동센터</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yellow_kr@naver.com</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>031-383-4398</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로227번길 48 7층, 온포인트 기능운동 센터</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_onpoint_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1442,7 +1362,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1463,17 +1383,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1304</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,46 +1402,30 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1327904427</t>
+          <t>7146714</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327904427</t>
+          <t>https://m.place.naver.com/place/7146714</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>피아트짐 헬스&amp;PT 평촌점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>stuff7561@naver.com</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1383-7998</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관평로182번길 48 신세대상가 지하1층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1561,13 +1465,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>972</v>
+        <v>0</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,51 +1480,35 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2047793712</t>
+          <t>2400001</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047793712</t>
+          <t>https://m.place.naver.com/place/2400001</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>하이엔드짐PT&amp;AT 안양 호계점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>highendgym_anyang1@naver.com</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1406-7009</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 경수대로 590 6층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/highendgym_anyang1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1630,12 +1518,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1651,17 +1539,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,765 +1558,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1441649714</t>
+          <t>7072653</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1441649714</t>
+          <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>아루카PT&amp;필라테스 범계점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>tkakrnlxla@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1348-6494</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 평촌대로223번길 43 501,502호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/tkakrnlxla</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>275</v>
-      </c>
-      <c r="R14" t="n">
-        <v>408</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1591259477</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1591259477</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>짐위드24 PT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>pmfpt@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1522-5102</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 동편로183번길 67-5 1층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.pmfpt.com/27</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>137</v>
-      </c>
-      <c r="R15" t="n">
-        <v>175</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1762568326</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1762568326</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>인싸짐 관양점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>mukiwihaeundoung@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 관악대로 346 2층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/inssagwanyang?igsh=MTR4d3VmNGt5eGw0ZA==</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>595</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2596</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3191</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1360937972</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1360937972</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>스포애니 범계역점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>spoany_24@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1413-9618</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 시민대로 167 안양벤처텔 10층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/spoany_24</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>2171</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2419</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4590</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>36123678</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/36123678</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>더메이커짐 헬스&amp;PT 안양본점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>themakergym1211@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1414-1222</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 안양시 만안구 문예로 35 지하1층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/the.maker.gym_anyang</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>415</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1086</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1501</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1195111809</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1195111809</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>피트니스89 헬스&amp;PT 내손점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>fitness89_gym@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1375-9004</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 안양시 동안구 포일로 8 미성 빌딩 2층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fitness89_gym</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1336</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3331</v>
-      </c>
-      <c r="R19" t="n">
-        <v>4667</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1471306408</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1471306408</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>테이스트피트니스 헬스&amp;PT 24시 안양예술공원점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>tasteay@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1330-9025</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 안양시 만안구 경수대로 1176 4층 테이스트 피트니스 안양예술공원점</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://pf.kakao.com/_xkhxhDn</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>262</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>27</v>
-      </c>
-      <c r="R20" t="n">
-        <v>289</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2028902532</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2028902532</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>소마핏 PT &amp; 필라테스</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>somafit233@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1313-8267</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 안양시 만안구 안양천서로 233 2층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://somafit.imweb.me/</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>275</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>620</v>
-      </c>
-      <c r="R21" t="n">
-        <v>895</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1655672347</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1655672347</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김관장의착한PT 관양동점</t>
+          <t>바른몸PT케어센터</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>yk8307@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1475-3481</t>
+          <t>0507-1396-6681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
+          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5director.kim</t>
+          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wit2oyw</t>
+          <t>https://talk.naver.com/ct/wc2d7d</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="R2" t="n">
-        <v>491</v>
+        <v>588</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2033189234</t>
+          <t>1754809694</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033189234</t>
+          <t>https://m.place.naver.com/place/1754809694</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김관장의착한PT 호계동점</t>
+          <t>헬스&amp;PT 하이얼짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>higher_gym1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1393-3519</t>
+          <t>0507-1303-2298</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
+          <t>경기 안양시 만안구 전파로 24 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thekindpt2</t>
+          <t>https://blog.naver.com/higher_gym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5trfo</t>
+          <t>https://talk.naver.com/ct/whocbqe</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1793</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
-        <v>672</v>
+        <v>23</v>
       </c>
       <c r="R3" t="n">
-        <v>2465</v>
+        <v>49</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1954358336</t>
+          <t>2037213524</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954358336</t>
+          <t>https://m.place.naver.com/place/2037213524</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="Q4" t="n">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="R4" t="n">
-        <v>2672</v>
+        <v>2679</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="Q5" t="n">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="R5" t="n">
-        <v>2620</v>
+        <v>2622</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바른몸PT케어센터</t>
+          <t>김관장의착한PT 관양동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yk8307@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1396-6681</t>
+          <t>0507-1475-3481</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
+          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
+          <t>https://www.instagram.com/5director.kim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc2d7d</t>
+          <t>https://talk.naver.com/ct/wit2oyw</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="Q2" t="n">
-        <v>462</v>
+        <v>412</v>
       </c>
       <c r="R2" t="n">
-        <v>588</v>
+        <v>491</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1754809694</t>
+          <t>2033189234</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754809694</t>
+          <t>https://m.place.naver.com/place/2033189234</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 하이얼짐</t>
+          <t>김관장의착한PT 호계동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>higher_gym1@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1303-2298</t>
+          <t>0507-1393-3519</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 전파로 24 3층</t>
+          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/higher_gym1</t>
+          <t>https://blog.naver.com/thekindpt2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whocbqe</t>
+          <t>https://talk.naver.com/ct/w5trfo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>1802</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>672</v>
       </c>
       <c r="R3" t="n">
-        <v>49</v>
+        <v>2474</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2037213524</t>
+          <t>1954358336</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037213524</t>
+          <t>https://m.place.naver.com/place/1954358336</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -851,36 +851,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>비오엠 범계점 PT 헬스</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>fitnessbom@naver.com</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1374-5144</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +874,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cd0d</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1357</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2622</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +914,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1206984359</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206984359</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1012,12 +992,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7507565</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7507565</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1090,12 +1070,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7189523</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7189523</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1168,12 +1148,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2500001</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2500001</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,12 +1226,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7482626</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7482626</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,12 +1304,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2900001</t>
+          <t>7146714</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2900001</t>
+          <t>https://m.place.naver.com/place/7146714</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,12 +1382,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7146714</t>
+          <t>2400001</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7146714</t>
+          <t>https://m.place.naver.com/place/2400001</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1480,93 +1460,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>7072653</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7072653</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7072653</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 관악대로 340 2층, 지하 1층</t>
+          <t>경기도 안양시 동안구 관악대로 340 2층, 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,32 +606,28 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wit2oyw</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q2" t="n">
         <v>412</v>
       </c>
       <c r="R2" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 흥안대로109번길 16 2층</t>
+          <t>경기도 안양시 동안구 흥안대로109번길 16 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,32 +700,28 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5trfo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="Q3" t="n">
         <v>672</v>
       </c>
       <c r="R3" t="n">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>경기도 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cnd9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -851,20 +839,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>비오엠 범계점 PT 헬스</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fitnessbom@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1374-5144</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessbom</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -895,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1265</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1358</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2623</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7507565</t>
+          <t>1206984359</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7507565</t>
+          <t>https://m.place.naver.com/place/1206984359</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -992,12 +996,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7189523</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7189523</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1070,12 +1074,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2500001</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2500001</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,12 +1152,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7482626</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7482626</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,12 +1230,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2900001</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2900001</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1304,12 +1308,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7146714</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7146714</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1382,12 +1386,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>7146714</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/7146714</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1460,15 +1464,93 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>2400001</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2400001</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>7072653</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김관장의착한PT 관양동점</t>
+          <t>바른몸PT케어센터</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>yk8307@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1475-3481</t>
+          <t>0507-1396-6681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관악대로 340 2층, 지하 1층</t>
+          <t>경기도 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5director.kim</t>
+          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="R2" t="n">
-        <v>494</v>
+        <v>588</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2033189234</t>
+          <t>1754809694</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033189234</t>
+          <t>https://m.place.naver.com/place/1754809694</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김관장의착한PT 호계동점</t>
+          <t>MN휘트니스 헬스 PT 골프 필라테스 범계점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>baeggops@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1393-3519</t>
+          <t>0507-1424-1777</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 흥안대로109번길 16 2층</t>
+          <t>경기도 안양시 동안구 평촌대로217번길 45 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thekindpt2</t>
+          <t>https://blog.naver.com/baeggops</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1803</v>
+        <v>1342</v>
       </c>
       <c r="Q3" t="n">
-        <v>672</v>
+        <v>956</v>
       </c>
       <c r="R3" t="n">
-        <v>2475</v>
+        <v>2298</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1954358336</t>
+          <t>1351894889</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954358336</t>
+          <t>https://m.place.naver.com/place/1351894889</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -812,10 +812,10 @@
         <v>1519</v>
       </c>
       <c r="Q4" t="n">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="R4" t="n">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바른몸PT케어센터</t>
+          <t>헬스코인 인덕원점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yk8307@naver.com</t>
+          <t>health_coin@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1396-6681</t>
+          <t>0507-1381-1413</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
+          <t>경기 안양시 동안구 흥안대로414번길 21-25 2층 헬스코인</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
+          <t>https://blog.naver.com/health_coin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4feal</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>126</v>
+        <v>466</v>
       </c>
       <c r="Q2" t="n">
-        <v>462</v>
+        <v>97</v>
       </c>
       <c r="R2" t="n">
-        <v>588</v>
+        <v>563</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1754809694</t>
+          <t>1286730922</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754809694</t>
+          <t>https://m.place.naver.com/place/1286730922</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MN휘트니스 헬스 PT 골프 필라테스 범계점</t>
+          <t>바른몸PT케어센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>baeggops@naver.com</t>
+          <t>yk8307@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1424-1777</t>
+          <t>0507-1396-6681</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 45 8층</t>
+          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baeggops</t>
+          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2d7d</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1342</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="n">
-        <v>956</v>
+        <v>462</v>
       </c>
       <c r="R3" t="n">
-        <v>2298</v>
+        <v>588</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,61 +738,45 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1351894889</t>
+          <t>1754809694</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1351894889</t>
+          <t>https://m.place.naver.com/place/1754809694</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>비오엠 안양점 PT 헬스 필라테스</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>fitnessbom2@naver.com</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1371-5144</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnFnxeK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -800,22 +792,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2680</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +816,35 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1685119758</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685119758</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>비오엠 범계점 PT 헬스</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>fitnessbom@naver.com</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1374-5144</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,12 +854,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +875,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1358</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2623</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +894,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1206984359</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206984359</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -996,17 +972,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7507565</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7507565</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1050,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7189523</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7189523</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,17 +1128,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2500001</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2500001</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1230,17 +1206,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7482626</t>
+          <t>7146714</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7482626</t>
+          <t>https://m.place.naver.com/place/7146714</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1284,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2900001</t>
+          <t>2400001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2900001</t>
+          <t>https://m.place.naver.com/place/2400001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1386,173 +1362,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7146714</t>
+          <t>7072653</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7146714</t>
+          <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2400001</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2400001</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7072653</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7072653</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스코인 인덕원점</t>
+          <t>김관장의착한PT 관양동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>health_coin@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1381-1413</t>
+          <t>0507-1475-3481</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 흥안대로414번길 21-25 2층 헬스코인</t>
+          <t>경기도 안양시 동안구 관악대로 340 2층, 지하 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/health_coin</t>
+          <t>https://www.instagram.com/5director.kim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,37 +601,33 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4feal</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="Q2" t="n">
-        <v>97</v>
+        <v>412</v>
       </c>
       <c r="R2" t="n">
-        <v>563</v>
+        <v>494</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1286730922</t>
+          <t>2033189234</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286730922</t>
+          <t>https://m.place.naver.com/place/2033189234</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>바른몸PT케어센터</t>
+          <t>김관장의착한PT 호계동점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>yk8307@naver.com</t>
+          <t>thekindpt2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1396-6681</t>
+          <t>0507-1393-3519</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
+          <t>경기도 안양시 동안구 흥안대로109번길 16 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
+          <t>https://blog.naver.com/thekindpt2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,37 +695,33 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc2d7d</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>126</v>
+        <v>1803</v>
       </c>
       <c r="Q3" t="n">
-        <v>462</v>
+        <v>672</v>
       </c>
       <c r="R3" t="n">
-        <v>588</v>
+        <v>2475</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1754809694</t>
+          <t>1954358336</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754809694</t>
+          <t>https://m.place.naver.com/place/1954358336</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -753,30 +745,46 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>비오엠 안양점 PT 헬스 필라테스</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fitnessbom2@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1371-5144</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xnFnxeK</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -792,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1161</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7507565</t>
+          <t>1685119758</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7507565</t>
+          <t>https://m.place.naver.com/place/1685119758</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -831,20 +839,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>비오엠 범계점 PT 헬스</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fitnessbom@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1374-5144</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기도 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessbom</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -854,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -875,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1264</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2623</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -894,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7189523</t>
+          <t>1206984359</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7189523</t>
+          <t>https://m.place.naver.com/place/1206984359</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -972,12 +996,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2500001</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2500001</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,12 +1074,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7482626</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7482626</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,12 +1152,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2900001</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2900001</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1206,12 +1230,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7146714</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7146714</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1284,12 +1308,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1362,15 +1386,171 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>7146714</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7146714</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2400001</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2400001</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>7072653</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>김관장의착한PT 관양동점</t>
+          <t>바른몸PT케어센터</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>yk8307@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1475-3481</t>
+          <t>0507-1396-6681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 관악대로 340 2층, 지하 1층</t>
+          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5director.kim</t>
+          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2d7d</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="Q2" t="n">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="R2" t="n">
-        <v>494</v>
+        <v>588</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2033189234</t>
+          <t>1754809694</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033189234</t>
+          <t>https://m.place.naver.com/place/1754809694</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김관장의착한PT 호계동점</t>
+          <t>레몬짐 안양점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>thekindpt2@naver.com</t>
+          <t>lafcompany_@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1393-3519</t>
+          <t>031-441-7779</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 흥안대로109번길 16 2층</t>
+          <t>경기 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thekindpt2</t>
+          <t>http://www.lemongym.co.kr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,13 +704,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzswuhw</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1803</v>
+        <v>635</v>
       </c>
       <c r="Q3" t="n">
-        <v>672</v>
+        <v>898</v>
       </c>
       <c r="R3" t="n">
-        <v>2475</v>
+        <v>1533</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1954358336</t>
+          <t>1417153496</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1954358336</t>
+          <t>https://m.place.naver.com/place/1417153496</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cnd9</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>O</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cd0d</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="Q5" t="n">
         <v>1359</v>
       </c>
       <c r="R5" t="n">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="Q5" t="n">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="R5" t="n">
-        <v>2624</v>
+        <v>2626</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바른몸PT케어센터</t>
+          <t>올데이피트니스365 안양점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yk8307@naver.com</t>
+          <t>tr_yoon@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1396-6681</t>
+          <t>0507-1357-8298</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
+          <t>경기도 안양시 만안구 양화로 16 4, 5, 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
+          <t>https://www.instagram.com/alldayfitness365_anyang/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,32 +606,28 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc2d7d</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>126</v>
+        <v>529</v>
       </c>
       <c r="Q2" t="n">
-        <v>462</v>
+        <v>1063</v>
       </c>
       <c r="R2" t="n">
-        <v>588</v>
+        <v>1592</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1754809694</t>
+          <t>1383802295</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754809694</t>
+          <t>https://m.place.naver.com/place/1383802295</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>레몬짐 안양점 PT&amp;헬스</t>
+          <t>짐위드24 PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lafcompany_@naver.com</t>
+          <t>pmfpt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>031-441-7779</t>
+          <t>1522-5102</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 태평로60번길 24 5층 501호, 502호, 505호, 506호, 507호</t>
+          <t>경기도 안양시 동안구 동편로183번길 67-5 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://www.lemongym.co.kr</t>
+          <t>https://www.pmfpt.com/27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,32 +700,28 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzswuhw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>635</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="n">
-        <v>898</v>
+        <v>186</v>
       </c>
       <c r="R3" t="n">
-        <v>1533</v>
+        <v>229</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1417153496</t>
+          <t>1762568326</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1417153496</t>
+          <t>https://m.place.naver.com/place/1762568326</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -753,46 +745,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>비오엠 안양점 PT 헬스 필라테스</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>fitnessbom2@naver.com</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1371-5144</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnFnxeK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -802,32 +778,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cnd9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1161</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2680</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +808,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1685119758</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1685119758</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -851,36 +823,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>비오엠 범계점 PT 헬스</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>fitnessbom@naver.com</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1374-5144</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessbom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,24 +846,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cd0d</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,17 +867,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1266</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1360</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2626</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +886,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1206984359</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1206984359</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1012,12 +964,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>7507565</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7507565</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1090,12 +1042,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7189523</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7189523</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1168,12 +1120,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2500001</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2500001</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,12 +1198,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7482626</t>
+          <t>7146714</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7482626</t>
+          <t>https://m.place.naver.com/place/7146714</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,12 +1276,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2900001</t>
+          <t>2400001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2900001</t>
+          <t>https://m.place.naver.com/place/2400001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1402,171 +1354,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>7146714</t>
+          <t>7072653</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7146714</t>
+          <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2400001</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2400001</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>7072653</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/7072653</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/안양_PT.xlsx
+++ b/naver-place-crawler/results_health/안양_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>올데이피트니스365 안양점</t>
+          <t>짐위드24 PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tr_yoon@naver.com</t>
+          <t>pmfpt@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1357-8298</t>
+          <t>1522-5102</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구 양화로 16 4, 5, 6층</t>
+          <t>경기 안양시 동안구 동편로183번길 67-5 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alldayfitness365_anyang/</t>
+          <t>https://www.pmfpt.com/27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wknk96r</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +621,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>529</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="n">
-        <v>1063</v>
+        <v>189</v>
       </c>
       <c r="R2" t="n">
-        <v>1592</v>
+        <v>232</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1383802295</t>
+          <t>1762568326</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1383802295</t>
+          <t>https://m.place.naver.com/place/1762568326</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,70 +662,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>짐위드24 PT</t>
+          <t>바른몸PT케어센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pmfpt@naver.com</t>
+          <t>yk8307@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1522-5102</t>
+          <t>0507-1396-6681</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 안양시 동안구 동편로183번길 67-5 1층</t>
+          <t>경기 안양시 동안구 시민대로 312 평촌칼라힐 빌딩 2층 232호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.pmfpt.com/27</t>
+          <t>https://www.instagram.com/barun_rehapnrecovery/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc2d7d</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="P3" t="n">
-        <v>43</v>
+        <v>126</v>
       </c>
       <c r="Q3" t="n">
-        <v>186</v>
+        <v>462</v>
       </c>
       <c r="R3" t="n">
-        <v>229</v>
+        <v>588</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,45 +738,61 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1762568326</t>
+          <t>1754809694</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1762568326</t>
+          <t>https://m.place.naver.com/place/1754809694</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>비오엠 안양점 PT 헬스 필라테스</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fitnessbom2@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1371-5144</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기 안양시 만안구 안양로 316 5층 505호, 507호, 508호 비오엠 안양점</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_xnFnxeK</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -778,28 +802,32 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cnd9</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2679</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -808,35 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>7507565</t>
+          <t>1685119758</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7507565</t>
+          <t>https://m.place.naver.com/place/1685119758</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>비오엠 범계점 PT 헬스</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>fitnessbom@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1374-5144</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>경기 안양시 동안구 평촌대로217번길 15 8층, 9층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitnessbom</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -846,20 +890,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cd0d</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -867,17 +915,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1270</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1361</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2631</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -886,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7189523</t>
+          <t>1206984359</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7189523</t>
+          <t>https://m.place.naver.com/place/1206984359</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -964,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2500001</t>
+          <t>7507565</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2500001</t>
+          <t>https://m.place.naver.com/place/7507565</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>7482626</t>
+          <t>7189523</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7482626</t>
+          <t>https://m.place.naver.com/place/7189523</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1168,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2900001</t>
+          <t>2500001</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2900001</t>
+          <t>https://m.place.naver.com/place/2500001</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1198,17 +1246,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7146714</t>
+          <t>7482626</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/7146714</t>
+          <t>https://m.place.naver.com/place/7482626</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1324,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2400001</t>
+          <t>2900001</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2400001</t>
+          <t>https://m.place.naver.com/place/2900001</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1354,17 +1402,173 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
+          <t>7146714</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/7146714</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2400001</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2400001</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>7072653</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/7072653</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
